--- a/resources/Пункты выдачи_import.xlsx
+++ b/resources/Пункты выдачи_import.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roman\Desktop\Дем\Dem\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roman\Desktop\На дем 1 вариант\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7020E684-C396-4464-B6C5-878D773A488C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CCF537-DE68-41C4-AE58-991168BD2AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2190" yWindow="1875" windowWidth="21525" windowHeight="11415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>344288, г. Лесной, ул. Чехова, 1</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t>190949, г. Лесной, ул. Мичурина, 26</t>
+  </si>
+  <si>
+    <t>pvz_id</t>
+  </si>
+  <si>
+    <t>address</t>
   </si>
 </sst>
 </file>
@@ -502,294 +508,305 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="40.875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
+      <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>35</v>
       </c>
     </row>
